--- a/netlify/template-files/customer-access-request.xlsx
+++ b/netlify/template-files/customer-access-request.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review and approval" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Document History" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -492,206 +492,130 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Version</t>
+          <t>Purpose</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>[x.x]</t>
+          <t>Records customer consent and limits when staff need to access a customer's account or data for support.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Document owner</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>[Role]</t>
+          <t>Support and engineering access to customer tenants.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Approver</t>
+          <t>Roles and responsibilities</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>[Role]</t>
+          <t>Support Lead: Requests and records consent.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Effective date</t>
-        </is>
-      </c>
+      <c r="A7" s="4" t="n"/>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>[YYYY-MM-DD]</t>
+          <t>Customer: Grants consent.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Next review date</t>
+          <t>Procedure</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>[YYYY-MM-DD]</t>
+          <t>1. Request customer permission in writing, stating purpose and duration.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
+      <c r="A9" s="4" t="n"/>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>2. Grant time-limited access (default [24 hours]).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>3. Log all actions taken.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
+      <c r="A11" s="4" t="n"/>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Records customer consent and limits when staff need to access a customer's account or data for support.</t>
+          <t>4. Revoke access at expiry and confirm to the customer.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>Frequency and timing</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Support and engineering access to customer tenants.</t>
+          <t>Each access.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Roles and responsibilities</t>
+          <t>Audit evidence checklist</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Support Lead: Requests and records consent.</t>
+          <t>☐ Sample requests with consent and revocation</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Framework mapping</t>
+        </is>
+      </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Customer: Grants consent.</t>
+          <t>ISO 27001: A.5.15, A.8.2</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Procedure</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>1. Request customer permission in writing, stating purpose and duration.</t>
-        </is>
-      </c>
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
       <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>2. Grant time-limited access (default [24 hours]).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>3. Log all actions taken.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>4. Revoke access at expiry and confirm to the customer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Frequency and timing</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Each access.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Audit evidence checklist</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>☐ Sample requests with consent and revocation</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Framework mapping</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>ISO 27001: A.5.15, A.8.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Template provided by OneLens by Ruchi. Replace all [bracketed] fields before use.</t>
         </is>
@@ -1274,106 +1198,67 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Version</t>
         </is>
       </c>
       <c r="B1" s="7" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C1" s="7" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Written by</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Approved by</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Prepared by</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Reviewed by</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Approved by</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Revision history</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Author</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Description of change</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>[YYYY-MM-DD]</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>[Role]</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Initial version</t>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[TODAYS DATE]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial Version</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[Name]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[Name]</t>
         </is>
       </c>
     </row>
